--- a/04_extract_results/extraction_quality_report.xlsx
+++ b/04_extract_results/extraction_quality_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,20 +456,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>filtered_candidate_sentences</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>high_relevance_sentences</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>medium_relevance_sentences</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>noise_sentences</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>avg_sentences_per_paper</t>
         </is>
@@ -489,18 +494,21 @@
         <v>1441</v>
       </c>
       <c r="E2" t="n">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="G2" t="n">
-        <v>230</v>
+        <v>94</v>
       </c>
       <c r="H2" t="n">
+        <v>239</v>
+      </c>
+      <c r="I2" t="n">
         <v>5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>60.04</v>
       </c>
     </row>

--- a/04_extract_results/extraction_quality_report.xlsx
+++ b/04_extract_results/extraction_quality_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,15 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>evidence_sentences</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>noise_sentences</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>avg_sentences_per_paper</t>
         </is>
@@ -491,25 +496,28 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1441</v>
+        <v>1913</v>
       </c>
       <c r="E2" t="n">
-        <v>333</v>
+        <v>603</v>
       </c>
       <c r="F2" t="n">
-        <v>333</v>
+        <v>603</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H2" t="n">
-        <v>239</v>
+        <v>507</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>346</v>
       </c>
       <c r="J2" t="n">
-        <v>60.04</v>
+        <v>8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>79.70999999999999</v>
       </c>
     </row>
   </sheetData>
